--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G453"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12647,6 +12647,87 @@
         <v>358.53</v>
       </c>
       <c r="G453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="C454" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="D454" t="n">
+        <v>341.97</v>
+      </c>
+      <c r="E454" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="F454" t="n">
+        <v>362.64</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="C455" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="D455" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="E455" t="n">
+        <v>341.68</v>
+      </c>
+      <c r="F455" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="C456" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="D456" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="E456" t="n">
+        <v>342.92</v>
+      </c>
+      <c r="F456" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="G456" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12663,7 +12744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17946,6 +18027,36 @@
       </c>
       <c r="B528" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -18114,28 +18225,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.388801619777452</v>
+        <v>-1.367980273492974</v>
       </c>
       <c r="J2" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K2" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.165847113086404</v>
+        <v>0.1633046263769206</v>
       </c>
       <c r="M2" t="n">
-        <v>18.13982916025102</v>
+        <v>18.11462603292712</v>
       </c>
       <c r="N2" t="n">
-        <v>577.3417471376472</v>
+        <v>575.3156776440212</v>
       </c>
       <c r="O2" t="n">
-        <v>24.02793680567783</v>
+        <v>23.98573904727601</v>
       </c>
       <c r="P2" t="n">
-        <v>354.1188042149492</v>
+        <v>353.9049494331678</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18192,28 +18303,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.393849196876642</v>
+        <v>-1.370147645436035</v>
       </c>
       <c r="J3" t="n">
+        <v>455</v>
+      </c>
+      <c r="K3" t="n">
         <v>452</v>
       </c>
-      <c r="K3" t="n">
-        <v>449</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2555336420558417</v>
+        <v>0.2505491525842031</v>
       </c>
       <c r="M3" t="n">
-        <v>13.31874019148117</v>
+        <v>13.32354331102497</v>
       </c>
       <c r="N3" t="n">
-        <v>336.0037142753085</v>
+        <v>336.0894789989602</v>
       </c>
       <c r="O3" t="n">
-        <v>18.33040409470856</v>
+        <v>18.33274335714544</v>
       </c>
       <c r="P3" t="n">
-        <v>350.3387652256853</v>
+        <v>350.0944563056531</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18270,28 +18381,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.293879384639617</v>
+        <v>-1.262478802081531</v>
       </c>
       <c r="J4" t="n">
+        <v>455</v>
+      </c>
+      <c r="K4" t="n">
         <v>452</v>
       </c>
-      <c r="K4" t="n">
-        <v>449</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2013183064494253</v>
+        <v>0.194276390963015</v>
       </c>
       <c r="M4" t="n">
-        <v>14.61527548059223</v>
+        <v>14.59220258440927</v>
       </c>
       <c r="N4" t="n">
-        <v>394.2698396396655</v>
+        <v>395.6254442160737</v>
       </c>
       <c r="O4" t="n">
-        <v>19.85622924020736</v>
+        <v>19.89033544755024</v>
       </c>
       <c r="P4" t="n">
-        <v>349.6405081429111</v>
+        <v>349.3168177476425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18348,28 +18459,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.187829836347038</v>
+        <v>-1.144819981233322</v>
       </c>
       <c r="J5" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K5" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1070953109369739</v>
+        <v>0.1006238578106567</v>
       </c>
       <c r="M5" t="n">
-        <v>18.97274239078093</v>
+        <v>18.98279129408347</v>
       </c>
       <c r="N5" t="n">
-        <v>696.8807692184204</v>
+        <v>699.6729961110188</v>
       </c>
       <c r="O5" t="n">
-        <v>26.39849937436635</v>
+        <v>26.45133259612867</v>
       </c>
       <c r="P5" t="n">
-        <v>341.904977722722</v>
+        <v>341.4612509266425</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18426,28 +18537,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1667124794771275</v>
+        <v>-0.170839636164537</v>
       </c>
       <c r="J6" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K6" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01223512798053517</v>
+        <v>0.01302395198221795</v>
       </c>
       <c r="M6" t="n">
-        <v>8.782897933627968</v>
+        <v>8.748810808190942</v>
       </c>
       <c r="N6" t="n">
-        <v>131.7671162201474</v>
+        <v>130.964949186381</v>
       </c>
       <c r="O6" t="n">
-        <v>11.47898585329503</v>
+        <v>11.44399183792006</v>
       </c>
       <c r="P6" t="n">
-        <v>371.3549294637586</v>
+        <v>371.3977558270137</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18485,7 +18596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G453"/>
+  <dimension ref="A1:G456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35209,6 +35320,117 @@
         </is>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-46.60352963956579,169.42063465449016</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-46.60359444163033,169.41974106018063</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-46.60371468560769,169.41885282380437</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-46.60381214269017,169.41796238416055</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-46.60402039396516,169.41708264862345</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-46.60352963956579,169.42063465449016</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-46.60355765973641,169.41973750508376</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-46.60368678519425,169.41885012744413</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-46.603772220874816,169.41795852647257</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-46.604033761045294,169.4170839401535</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-46.603483796768636,169.42063022310856</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-46.60352446631982,169.41973429682852</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-46.60367198272408,169.4188486969001</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-46.60378334515596,169.41795960142343</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-46.604033761045294,169.4170839401535</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12728,6 +12728,87 @@
         <v>364.13</v>
       </c>
       <c r="G456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>330</v>
+      </c>
+      <c r="C457" t="n">
+        <v>327.24</v>
+      </c>
+      <c r="D457" t="n">
+        <v>336.09</v>
+      </c>
+      <c r="E457" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="F457" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="C458" t="n">
+        <v>325.37</v>
+      </c>
+      <c r="D458" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="E458" t="n">
+        <v>331.37</v>
+      </c>
+      <c r="F458" t="n">
+        <v>361.39</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>324.85</v>
+      </c>
+      <c r="C459" t="n">
+        <v>323.85</v>
+      </c>
+      <c r="D459" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="E459" t="n">
+        <v>328.52</v>
+      </c>
+      <c r="F459" t="n">
+        <v>357.27</v>
+      </c>
+      <c r="G459" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12744,7 +12825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18057,6 +18138,36 @@
       </c>
       <c r="B531" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -18225,28 +18336,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.367980273492974</v>
+        <v>-1.354149868202615</v>
       </c>
       <c r="J2" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K2" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1633046263769206</v>
+        <v>0.1623565058331635</v>
       </c>
       <c r="M2" t="n">
-        <v>18.11462603292712</v>
+        <v>18.05757050887381</v>
       </c>
       <c r="N2" t="n">
-        <v>575.3156776440212</v>
+        <v>572.3547486062035</v>
       </c>
       <c r="O2" t="n">
-        <v>23.98573904727601</v>
+        <v>23.92393672885388</v>
       </c>
       <c r="P2" t="n">
-        <v>353.9049494331678</v>
+        <v>353.7620096285195</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18303,28 +18414,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.370147645436035</v>
+        <v>-1.354241147511632</v>
       </c>
       <c r="J3" t="n">
+        <v>458</v>
+      </c>
+      <c r="K3" t="n">
         <v>455</v>
       </c>
-      <c r="K3" t="n">
-        <v>452</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2505491525842031</v>
+        <v>0.2483680737914848</v>
       </c>
       <c r="M3" t="n">
-        <v>13.32354331102497</v>
+        <v>13.29717098796593</v>
       </c>
       <c r="N3" t="n">
-        <v>336.0894789989602</v>
+        <v>334.9097334607467</v>
       </c>
       <c r="O3" t="n">
-        <v>18.33274335714544</v>
+        <v>18.3005391576518</v>
       </c>
       <c r="P3" t="n">
-        <v>350.0944563056531</v>
+        <v>349.9294503957603</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18381,28 +18492,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.262478802081531</v>
+        <v>-1.240509797917025</v>
       </c>
       <c r="J4" t="n">
+        <v>458</v>
+      </c>
+      <c r="K4" t="n">
         <v>455</v>
       </c>
-      <c r="K4" t="n">
-        <v>452</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.194276390963015</v>
+        <v>0.1903312136558328</v>
       </c>
       <c r="M4" t="n">
-        <v>14.59220258440927</v>
+        <v>14.5475557356265</v>
       </c>
       <c r="N4" t="n">
-        <v>395.6254442160737</v>
+        <v>395.0245499773089</v>
       </c>
       <c r="O4" t="n">
-        <v>19.89033544755024</v>
+        <v>19.87522452646281</v>
       </c>
       <c r="P4" t="n">
-        <v>349.3168177476425</v>
+        <v>349.0889376197618</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18459,28 +18570,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.144819981233322</v>
+        <v>-1.116170822121136</v>
       </c>
       <c r="J5" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K5" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1006238578106567</v>
+        <v>0.09698901731092857</v>
       </c>
       <c r="M5" t="n">
-        <v>18.98279129408347</v>
+        <v>18.95131373128733</v>
       </c>
       <c r="N5" t="n">
-        <v>699.6729961110188</v>
+        <v>698.5201083300685</v>
       </c>
       <c r="O5" t="n">
-        <v>26.45133259612867</v>
+        <v>26.429530989597</v>
       </c>
       <c r="P5" t="n">
-        <v>341.4612509266425</v>
+        <v>341.1638634454424</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18537,28 +18648,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.170839636164537</v>
+        <v>-0.1774240193721214</v>
       </c>
       <c r="J6" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K6" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01302395198221795</v>
+        <v>0.01421230543640262</v>
       </c>
       <c r="M6" t="n">
-        <v>8.748810808190942</v>
+        <v>8.728894016101473</v>
       </c>
       <c r="N6" t="n">
-        <v>130.964949186381</v>
+        <v>130.3610188613782</v>
       </c>
       <c r="O6" t="n">
-        <v>11.44399183792006</v>
+        <v>11.41757499915714</v>
       </c>
       <c r="P6" t="n">
-        <v>371.3977558270137</v>
+        <v>371.4665751427651</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18596,7 +18707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35431,6 +35542,117 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-46.6034870263982,169.42063053529967</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-46.60352240294525,169.41973409739654</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-46.60366193498671,169.41884772586448</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-46.603750869431934,169.4179564632613</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-46.604051434298874,169.4170856477476</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-46.60347330047258,169.4206292084877</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-46.603505626813046,169.4197324759281</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-46.60362685761781,169.4188443359117</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-46.6036797278592,169.4179495887882</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-46.60400917997172,169.41708156512544</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-46.603440824753065,169.42062606923508</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-46.60349199059858,169.4197311579436</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-46.603598777780185,169.41884162221766</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-46.603654159954615,169.41794711814202</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-46.6039722186493,169.41707799391816</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
